--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133818735</v>
+        <v>133818496</v>
       </c>
       <c r="B2" t="n">
         <v>57958</v>
@@ -703,10 +703,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494189</v>
+        <v>494132</v>
       </c>
       <c r="R2" t="n">
-        <v>6805755</v>
+        <v>6805701</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133818496</v>
+        <v>133818735</v>
       </c>
       <c r="B3" t="n">
         <v>57958</v>
@@ -815,19 +824,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494132</v>
+        <v>494189</v>
       </c>
       <c r="R3" t="n">
-        <v>6805701</v>
+        <v>6805755</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1023,7 +1023,7 @@
         <v>133818630</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>133819313</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133819367</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>133819339</v>
       </c>
       <c r="B12" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>133818827</v>
       </c>
       <c r="B14" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -1817,44 +1817,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133819339</v>
+        <v>133819426</v>
       </c>
       <c r="B12" t="n">
-        <v>91940</v>
+        <v>57145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494230</v>
+        <v>494235</v>
       </c>
       <c r="R12" t="n">
-        <v>6805708</v>
+        <v>6805720</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,53 +1929,44 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133819426</v>
+        <v>133819339</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>91940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494235</v>
+        <v>494230</v>
       </c>
       <c r="R13" t="n">
-        <v>6805720</v>
+        <v>6805708</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133818496</v>
+        <v>133818735</v>
       </c>
       <c r="B2" t="n">
         <v>57958</v>
@@ -703,19 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494132</v>
+        <v>494189</v>
       </c>
       <c r="R2" t="n">
-        <v>6805701</v>
+        <v>6805755</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,14 +780,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133818735</v>
+        <v>133818496</v>
       </c>
       <c r="B3" t="n">
         <v>57958</v>
@@ -824,10 +815,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494189</v>
+        <v>494132</v>
       </c>
       <c r="R3" t="n">
-        <v>6805755</v>
+        <v>6805701</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1127,38 +1127,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133818536</v>
+        <v>133818785</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>5179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494188</v>
+        <v>494189</v>
       </c>
       <c r="R6" t="n">
-        <v>6805764</v>
+        <v>6805755</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,45 +1232,45 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133818785</v>
+        <v>133818536</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494189</v>
+        <v>494188</v>
       </c>
       <c r="R7" t="n">
-        <v>6805755</v>
+        <v>6805764</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
         <v>133819367</v>
       </c>
       <c r="B10" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1817,53 +1817,44 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133819426</v>
+        <v>133819339</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>91946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494235</v>
+        <v>494230</v>
       </c>
       <c r="R12" t="n">
-        <v>6805720</v>
+        <v>6805708</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,44 +1920,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133819339</v>
+        <v>133819426</v>
       </c>
       <c r="B13" t="n">
-        <v>91940</v>
+        <v>57145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494230</v>
+        <v>494235</v>
       </c>
       <c r="R13" t="n">
-        <v>6805708</v>
+        <v>6805720</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
         <v>133818827</v>
       </c>
       <c r="B14" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133818735</v>
+        <v>133818496</v>
       </c>
       <c r="B2" t="n">
         <v>57958</v>
@@ -703,10 +703,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494189</v>
+        <v>494132</v>
       </c>
       <c r="R2" t="n">
-        <v>6805755</v>
+        <v>6805701</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133818496</v>
+        <v>133818735</v>
       </c>
       <c r="B3" t="n">
         <v>57958</v>
@@ -815,19 +824,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494132</v>
+        <v>494189</v>
       </c>
       <c r="R3" t="n">
-        <v>6805701</v>
+        <v>6805755</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1127,38 +1127,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133818785</v>
+        <v>133818536</v>
       </c>
       <c r="B6" t="n">
-        <v>5179</v>
+        <v>57958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494189</v>
+        <v>494188</v>
       </c>
       <c r="R6" t="n">
-        <v>6805755</v>
+        <v>6805764</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,38 +1239,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133818536</v>
+        <v>133818785</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>5179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494188</v>
+        <v>494189</v>
       </c>
       <c r="R7" t="n">
-        <v>6805764</v>
+        <v>6805755</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
         <v>133819367</v>
       </c>
       <c r="B10" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
         <v>133819339</v>
       </c>
       <c r="B12" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
         <v>133818827</v>
       </c>
       <c r="B14" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133818496</v>
+        <v>133818735</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,19 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494132</v>
+        <v>494189</v>
       </c>
       <c r="R2" t="n">
-        <v>6805701</v>
+        <v>6805755</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133818735</v>
+        <v>133818496</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +815,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494189</v>
+        <v>494132</v>
       </c>
       <c r="R3" t="n">
-        <v>6805755</v>
+        <v>6805701</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +911,7 @@
         <v>133819267</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>133818630</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,38 +1127,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133818536</v>
+        <v>133818785</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>5181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494188</v>
+        <v>494189</v>
       </c>
       <c r="R6" t="n">
-        <v>6805764</v>
+        <v>6805755</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,45 +1232,45 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133818785</v>
+        <v>133818536</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>57965</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494189</v>
+        <v>494188</v>
       </c>
       <c r="R7" t="n">
-        <v>6805755</v>
+        <v>6805764</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
         <v>133819313</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>133819829</v>
       </c>
       <c r="B9" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133819367</v>
       </c>
       <c r="B10" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>133819627</v>
       </c>
       <c r="B11" t="n">
-        <v>6274</v>
+        <v>6286</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>133819339</v>
       </c>
       <c r="B12" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>133819426</v>
       </c>
       <c r="B13" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>133818827</v>
       </c>
       <c r="B14" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133818735</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133818496</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>133819267</v>
       </c>
       <c r="B4" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>133818630</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
         <v>133818536</v>
       </c>
       <c r="B7" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>133819313</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>133819829</v>
       </c>
       <c r="B9" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133819367</v>
       </c>
       <c r="B10" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>133819339</v>
       </c>
       <c r="B12" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>133819426</v>
       </c>
       <c r="B13" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>133818827</v>
       </c>
       <c r="B14" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133818735</v>
+        <v>133818496</v>
       </c>
       <c r="B2" t="n">
         <v>57975</v>
@@ -703,10 +703,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494189</v>
+        <v>494132</v>
       </c>
       <c r="R2" t="n">
-        <v>6805755</v>
+        <v>6805701</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133818496</v>
+        <v>133818735</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -815,19 +824,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494132</v>
+        <v>494189</v>
       </c>
       <c r="R3" t="n">
-        <v>6805701</v>
+        <v>6805755</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133818496</v>
+        <v>133818735</v>
       </c>
       <c r="B2" t="n">
         <v>57975</v>
@@ -703,19 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494132</v>
+        <v>494189</v>
       </c>
       <c r="R2" t="n">
-        <v>6805701</v>
+        <v>6805755</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133818735</v>
+        <v>133818496</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -824,10 +815,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494189</v>
+        <v>494132</v>
       </c>
       <c r="R3" t="n">
-        <v>6805755</v>
+        <v>6805701</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>133818630</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
         <v>133819313</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133819367</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>133819339</v>
       </c>
       <c r="B12" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>133818827</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>133818630</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,38 +1127,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133818785</v>
+        <v>133818536</v>
       </c>
       <c r="B6" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494189</v>
+        <v>494188</v>
       </c>
       <c r="R6" t="n">
-        <v>6805755</v>
+        <v>6805764</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,38 +1239,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133818536</v>
+        <v>133818785</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>5181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494188</v>
+        <v>494189</v>
       </c>
       <c r="R7" t="n">
-        <v>6805764</v>
+        <v>6805755</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
         <v>133819313</v>
       </c>
       <c r="B8" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>133819367</v>
       </c>
       <c r="B10" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
         <v>133819339</v>
       </c>
       <c r="B12" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>133818827</v>
       </c>
       <c r="B14" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133818735</v>
+        <v>133818827</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>91937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494189</v>
+        <v>494215</v>
       </c>
       <c r="R2" t="n">
-        <v>6805755</v>
+        <v>6805734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,59 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133818496</v>
+        <v>133819367</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>91937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494132</v>
+        <v>494230</v>
       </c>
       <c r="R3" t="n">
-        <v>6805701</v>
+        <v>6805708</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -871,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,50 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133819267</v>
+        <v>133818630</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494230</v>
+        <v>494189</v>
       </c>
       <c r="R4" t="n">
-        <v>6805704</v>
+        <v>6805755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,14 +996,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133818630</v>
+        <v>133819313</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1055,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494189</v>
+        <v>494230</v>
       </c>
       <c r="R5" t="n">
-        <v>6805755</v>
+        <v>6805708</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1076,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133818536</v>
+        <v>133818496</v>
       </c>
       <c r="B6" t="n">
         <v>57975</v>
@@ -1155,10 +1136,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1167,13 +1157,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494188</v>
+        <v>494132</v>
       </c>
       <c r="R6" t="n">
-        <v>6805764</v>
+        <v>6805701</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,38 +1229,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133818785</v>
+        <v>133818536</v>
       </c>
       <c r="B7" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494189</v>
+        <v>494188</v>
       </c>
       <c r="R7" t="n">
-        <v>6805755</v>
+        <v>6805764</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133819313</v>
+        <v>133818735</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,37 +1352,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494230</v>
+        <v>494189</v>
       </c>
       <c r="R8" t="n">
-        <v>6805708</v>
+        <v>6805755</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1431,12 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,52 +1453,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133819829</v>
+        <v>133819267</v>
       </c>
       <c r="B9" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1517,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494234</v>
+        <v>494230</v>
       </c>
       <c r="R9" t="n">
-        <v>6805756</v>
+        <v>6805704</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133819367</v>
+        <v>133819426</v>
       </c>
       <c r="B10" t="n">
-        <v>91930</v>
+        <v>57162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1600,37 +1576,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494230</v>
+        <v>494235</v>
       </c>
       <c r="R10" t="n">
-        <v>6805708</v>
+        <v>6805720</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1696,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133819627</v>
+        <v>133819829</v>
       </c>
       <c r="B11" t="n">
-        <v>6286</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,21 +1688,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105336</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1731,7 +1712,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1740,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494227</v>
+        <v>494234</v>
       </c>
       <c r="R11" t="n">
-        <v>6805730</v>
+        <v>6805756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,12 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Klibbticka gammal låga</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,41 +1803,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133819339</v>
+        <v>133818785</v>
       </c>
       <c r="B12" t="n">
-        <v>91987</v>
+        <v>5181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mellanberg, Mellanberg, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494230</v>
+        <v>494189</v>
       </c>
       <c r="R12" t="n">
-        <v>6805708</v>
+        <v>6805755</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1883,7 +1878,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133819426</v>
+        <v>133819627</v>
       </c>
       <c r="B13" t="n">
-        <v>57162</v>
+        <v>6286</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,27 +1926,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>105336</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1960,13 +1959,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494235</v>
+        <v>494227</v>
       </c>
       <c r="R13" t="n">
-        <v>6805720</v>
+        <v>6805730</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1995,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2004,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Klibbticka gammal låga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,113 +2033,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>133818827</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91930</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Mellanberg, Mellanberg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>494215</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6805734</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21799-2026 artfynd.xlsx
+++ b/artfynd/A 21799-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133818827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133819367</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133818630</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133819313</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133818496</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133818536</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133818735</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1562,6 +1602,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133819267</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133819426</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,6 +1850,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133819829</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133818785</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,8 +2093,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133819627</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>